--- a/DB_SCHEMA_20251105.xlsx
+++ b/DB_SCHEMA_20251105.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\舊電腦複製\備份_20220215\project\22_凱鈿_合作案\01_Develop\Pharmacy_Test_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050FEEB6-AE42-4C7E-8653-FEF83191C7FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2EB9F2-E7EC-4DC4-95FD-BE832A5F8421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="清單" sheetId="1" r:id="rId1"/>
@@ -129,9 +129,6 @@
     <t>CASH_BALANCE</t>
   </si>
   <si>
-    <t>DECIMAL(10, 2)</t>
-  </si>
-  <si>
     <t>使用者目前結算餘額
 需透過系統設定取得結算日期(Key為USER_CASH_BALANCE_SETTLEMENT_TIME)，扣掉超過結算日期的交易紀錄金額，會和目前餘額相同</t>
   </si>
@@ -291,15 +288,20 @@
     <t>KEY</t>
   </si>
   <si>
+    <t>VALUE</t>
+  </si>
+  <si>
+    <t>系統設定值</t>
+  </si>
+  <si>
     <t>系統設定KEY
 USER_CASH_BALANCE_SETTLEMENT_TIME：使用者餘額結算時間
 PHARMACY_STOCK_SETTLEMENT_TIME：藥局餘額結算時間</t>
-  </si>
-  <si>
-    <t>VALUE</t>
-  </si>
-  <si>
-    <t>系統設定值</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>decimal(10, 2)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -773,10 +775,10 @@
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" ht="16.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -904,7 +906,7 @@
     <col min="7" max="7" width="25.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" ht="16.2">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -917,7 +919,7 @@
       <c r="F1" s="24"/>
       <c r="G1" s="22"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" ht="16.2">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -966,7 +968,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" ht="16.2">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -987,7 +989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" ht="16.2">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -1004,7 +1006,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" ht="113.4">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -1012,64 +1014,64 @@
         <v>32</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
       <c r="F7" s="16"/>
       <c r="G7" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16.2">
       <c r="A8" s="12">
         <v>4</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
       <c r="G8" s="19" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="16.2">
       <c r="A9" s="12">
         <v>5</v>
       </c>
       <c r="B9" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="17" t="s">
         <v>37</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>38</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
       <c r="F9" s="20"/>
       <c r="G9" s="17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="16.2">
       <c r="A10" s="12">
         <v>6</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="20"/>
       <c r="G10" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1098,7 +1100,7 @@
     <col min="7" max="7" width="25.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" ht="16.2">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1111,7 +1113,7 @@
       <c r="F1" s="24"/>
       <c r="G1" s="22"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" ht="16.2">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1160,12 +1162,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" ht="16.2">
       <c r="A5" s="12">
         <v>1</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>27</v>
@@ -1181,7 +1183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" ht="16.2">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -1195,10 +1197,10 @@
       <c r="E6" s="16"/>
       <c r="F6" s="16"/>
       <c r="G6" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="113.4">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -1206,64 +1208,64 @@
         <v>32</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
       <c r="F7" s="16"/>
       <c r="G7" s="14" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16.2">
       <c r="A8" s="12">
         <v>4</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="18"/>
       <c r="F8" s="18"/>
       <c r="G8" s="19" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="16.2">
       <c r="A9" s="12">
         <v>5</v>
       </c>
       <c r="B9" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="17" t="s">
         <v>37</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>38</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
       <c r="F9" s="20"/>
       <c r="G9" s="17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="16.2">
       <c r="A10" s="12">
         <v>6</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="20"/>
       <c r="G10" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1292,7 +1294,7 @@
     <col min="7" max="7" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" ht="16.2">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1305,7 +1307,7 @@
       <c r="F1" s="24"/>
       <c r="G1" s="22"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" ht="16.2">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1354,12 +1356,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" ht="16.2">
       <c r="A5" s="12">
         <v>1</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>27</v>
@@ -1375,12 +1377,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" ht="32.4">
       <c r="A6" s="12">
         <v>2</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>27</v>
@@ -1389,35 +1391,35 @@
       <c r="E6" s="16"/>
       <c r="F6" s="16"/>
       <c r="G6" s="14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="129.6">
       <c r="A7" s="12">
         <v>3</v>
       </c>
       <c r="B7" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>48</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>49</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
       <c r="F7" s="16"/>
       <c r="G7" s="14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="32.4">
       <c r="A8" s="12">
         <v>4</v>
       </c>
       <c r="B8" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>51</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>52</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>28</v>
@@ -1425,18 +1427,18 @@
       <c r="E8" s="16"/>
       <c r="F8" s="16"/>
       <c r="G8" s="14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="32.4">
       <c r="A9" s="12">
         <v>5</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>28</v>
@@ -1444,24 +1446,24 @@
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="G9" s="14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="64.8">
       <c r="A10" s="12">
         <v>6</v>
       </c>
       <c r="B10" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>56</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>57</v>
       </c>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
       <c r="G10" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1488,7 +1490,7 @@
     <col min="3" max="3" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" ht="16.2">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1501,7 +1503,7 @@
       <c r="F1" s="24"/>
       <c r="G1" s="22"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" ht="16.2">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1550,12 +1552,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" ht="16.2">
       <c r="A5" s="12">
         <v>1</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>27</v>
@@ -1571,7 +1573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" ht="32.4">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -1579,13 +1581,13 @@
         <v>29</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D6" s="16"/>
       <c r="E6" s="16"/>
       <c r="F6" s="16"/>
       <c r="G6" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1614,7 +1616,7 @@
     <col min="7" max="7" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" ht="16.2">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1627,7 +1629,7 @@
       <c r="F1" s="24"/>
       <c r="G1" s="22"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" ht="16.2">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1676,12 +1678,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" ht="16.2">
       <c r="A5" s="12">
         <v>1</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>27</v>
@@ -1697,12 +1699,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" ht="16.2">
       <c r="A6" s="12">
         <v>2</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>27</v>
@@ -1711,15 +1713,15 @@
       <c r="E6" s="16"/>
       <c r="F6" s="16"/>
       <c r="G6" s="13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="16.2">
       <c r="A7" s="12">
         <v>3</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>27</v>
@@ -1728,58 +1730,58 @@
       <c r="E7" s="16"/>
       <c r="F7" s="16"/>
       <c r="G7" s="13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16.2">
       <c r="A8" s="12">
         <v>4</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
       <c r="F8" s="16"/>
       <c r="G8" s="13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="16.2">
       <c r="A9" s="12">
         <v>5</v>
       </c>
       <c r="B9" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="17" t="s">
         <v>37</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>38</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
       <c r="F9" s="20"/>
       <c r="G9" s="17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="16.2">
       <c r="A10" s="12">
         <v>6</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="20"/>
       <c r="G10" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1808,7 +1810,7 @@
     <col min="7" max="7" width="51.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" ht="16.2">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1821,13 +1823,13 @@
       <c r="F1" s="24"/>
       <c r="G1" s="22"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" ht="16.2">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D2" s="28"/>
       <c r="E2" s="28"/>
@@ -1870,12 +1872,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" ht="16.2">
       <c r="A5" s="12">
         <v>1</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>27</v>
@@ -1891,12 +1893,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" ht="16.2">
       <c r="A6" s="12">
         <v>2</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>27</v>
@@ -1905,15 +1907,15 @@
       <c r="E6" s="16"/>
       <c r="F6" s="16"/>
       <c r="G6" s="13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="16.2">
       <c r="A7" s="12">
         <v>3</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>27</v>
@@ -1922,41 +1924,41 @@
       <c r="E7" s="16"/>
       <c r="F7" s="16"/>
       <c r="G7" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16.2">
       <c r="A8" s="12">
         <v>4</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
       <c r="F8" s="16"/>
       <c r="G8" s="13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="48.6">
       <c r="A9" s="12">
         <v>5</v>
       </c>
       <c r="B9" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="19" t="s">
         <v>37</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>38</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
       <c r="F9" s="20"/>
       <c r="G9" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1985,7 +1987,7 @@
     <col min="7" max="7" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" ht="16.2">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1998,7 +2000,7 @@
       <c r="F1" s="24"/>
       <c r="G1" s="22"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" ht="16.2">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -2047,12 +2049,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" ht="16.2">
       <c r="A5" s="12">
         <v>1</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>27</v>
@@ -2068,7 +2070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" ht="16.2">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2082,15 +2084,15 @@
       <c r="E6" s="16"/>
       <c r="F6" s="16"/>
       <c r="G6" s="13" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="16.2">
       <c r="A7" s="12">
         <v>3</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>27</v>
@@ -2099,32 +2101,32 @@
       <c r="E7" s="16"/>
       <c r="F7" s="16"/>
       <c r="G7" s="13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16.2">
       <c r="A8" s="12">
         <v>4</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
       <c r="F8" s="16"/>
       <c r="G8" s="13" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="16.2">
       <c r="A9" s="12">
         <v>5</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>27</v>
@@ -2133,41 +2135,41 @@
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="G9" s="13" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="48.6">
       <c r="A10" s="12">
         <v>6</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
       <c r="G10" s="13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="48.6">
       <c r="A11" s="12">
         <v>7</v>
       </c>
       <c r="B11" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="19" t="s">
         <v>37</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>38</v>
       </c>
       <c r="D11" s="20"/>
       <c r="E11" s="20"/>
       <c r="F11" s="20"/>
       <c r="G11" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -2196,7 +2198,7 @@
     <col min="7" max="7" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" ht="16.2">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -2209,7 +2211,7 @@
       <c r="F1" s="24"/>
       <c r="G1" s="22"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" ht="16.2">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -2258,12 +2260,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" ht="16.2">
       <c r="A5" s="12">
         <v>1</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>27</v>
@@ -2279,12 +2281,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" ht="81">
       <c r="A6" s="12">
         <v>2</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>30</v>
@@ -2292,16 +2294,16 @@
       <c r="D6" s="15"/>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
-      <c r="G6" s="13" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="G6" s="14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="16.2">
       <c r="A7" s="12">
         <v>3</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>30</v>
@@ -2310,41 +2312,41 @@
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
       <c r="G7" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16.2">
       <c r="A8" s="12">
         <v>4</v>
       </c>
       <c r="B8" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="17" t="s">
         <v>37</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>38</v>
       </c>
       <c r="D8" s="20"/>
       <c r="E8" s="20"/>
       <c r="F8" s="20"/>
       <c r="G8" s="17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="16.2">
       <c r="A9" s="12">
         <v>5</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
       <c r="F9" s="20"/>
       <c r="G9" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
